--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T11:00:33+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T11:53:44+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:53:44+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T12:55:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T12:55:48+01:00</t>
+    <t>2026-03-18T17:09:19+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$139</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4728" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4537" uniqueCount="640">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T11:10:04+02:00</t>
+    <t>2026-06-24T16:51:19+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -812,7 +812,7 @@
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://loinc.org"/&gt;
   &lt;code value="9843-4"/&gt;
-  &lt;display value="Head Occipital-frontal circumference"/&gt;
+  &lt;display value="Kopfumfang okzipital-frontal"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
@@ -1109,38 +1109,20 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.kbv.de/StructureDefinition/KBV_PR_WEST_Encounter|1.0.0-kommentierung)
+    <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
   <si>
-    <t>Begegnung</t>
-  </si>
-  <si>
-    <t>Referenz zur Ressource Begegnung</t>
+    <t>Healthcare event during which this observation is made</t>
+  </si>
+  <si>
+    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
   </si>
   <si>
     <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
-  </si>
-  <si>
-    <t>Observation.encounter.id</t>
-  </si>
-  <si>
-    <t>Observation.encounter.extension</t>
-  </si>
-  <si>
-    <t>Observation.encounter.reference</t>
-  </si>
-  <si>
-    <t>Observation.encounter.type</t>
-  </si>
-  <si>
-    <t>Observation.encounter.identifier</t>
-  </si>
-  <si>
-    <t>Observation.encounter.display</t>
   </si>
   <si>
     <t>Observation.effective[x]</t>
@@ -2363,7 +2345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ145"/>
+  <dimension ref="A1:AJ139"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.15625" customWidth="true" bestFit="true"/>
@@ -7945,7 +7927,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>344</v>
       </c>
@@ -7961,10 +7943,10 @@
         <v>74</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>76</v>
@@ -8058,35 +8040,39 @@
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>76</v>
+        <v>352</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>97</v>
+        <v>353</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>98</v>
+        <v>354</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
       </c>
@@ -8122,19 +8108,17 @@
         <v>76</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>76</v>
+        <v>359</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>100</v>
+        <v>351</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -8143,52 +8127,56 @@
         <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>76</v>
+        <v>360</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="D57" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>103</v>
+        <v>353</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>104</v>
+        <v>354</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>105</v>
+        <v>363</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
       </c>
@@ -8224,39 +8212,39 @@
         <v>76</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>110</v>
+        <v>351</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>111</v>
+        <v>360</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8264,13 +8252,13 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>76</v>
@@ -8279,16 +8267,16 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>317</v>
+        <v>365</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>318</v>
+        <v>366</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>319</v>
+        <v>367</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8338,7 +8326,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>320</v>
+        <v>364</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
@@ -8347,7 +8335,7 @@
         <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>321</v>
+        <v>94</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>95</v>
@@ -8355,10 +8343,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8381,18 +8369,20 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>124</v>
+        <v>369</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>323</v>
+        <v>370</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>324</v>
+        <v>371</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
       </c>
@@ -8416,13 +8406,13 @@
         <v>76</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>326</v>
+        <v>76</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>327</v>
+        <v>76</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>76</v>
@@ -8440,27 +8430,27 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>95</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8471,10 +8461,10 @@
         <v>74</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>76</v>
@@ -8483,18 +8473,20 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>193</v>
+        <v>374</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>76</v>
       </c>
@@ -8530,19 +8522,17 @@
         <v>76</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>76</v>
+        <v>359</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>333</v>
+        <v>373</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
@@ -8551,20 +8541,22 @@
         <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>94</v>
+        <v>379</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>76</v>
       </c>
@@ -8573,10 +8565,10 @@
         <v>74</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>76</v>
@@ -8585,18 +8577,20 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>97</v>
+        <v>374</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>335</v>
+        <v>375</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>76</v>
       </c>
@@ -8605,7 +8599,7 @@
         <v>76</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>76</v>
+        <v>383</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>76</v>
@@ -8620,13 +8614,11 @@
         <v>76</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>76</v>
+        <v>384</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>76</v>
@@ -8644,7 +8636,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>338</v>
+        <v>373</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>74</v>
@@ -8653,7 +8645,7 @@
         <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>94</v>
+        <v>379</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>95</v>
@@ -8661,46 +8653,42 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>358</v>
+        <v>76</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>359</v>
+        <v>97</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>360</v>
+        <v>98</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>76</v>
       </c>
@@ -8736,17 +8724,19 @@
         <v>76</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AC62" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>365</v>
+        <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>357</v>
+        <v>100</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>74</v>
@@ -8755,56 +8745,52 @@
         <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>366</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>358</v>
+        <v>102</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>359</v>
+        <v>103</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>360</v>
+        <v>104</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>369</v>
+        <v>105</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>76</v>
       </c>
@@ -8840,39 +8826,39 @@
         <v>76</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>357</v>
+        <v>110</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>366</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8880,13 +8866,13 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>76</v>
@@ -8895,18 +8881,20 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>118</v>
+        <v>391</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>76</v>
       </c>
@@ -8954,7 +8942,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>74</v>
@@ -8971,10 +8959,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8991,30 +8979,32 @@
         <v>76</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>375</v>
+        <v>162</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>202</v>
+        <v>273</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q65" s="2"/>
+      <c r="Q65" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="R65" t="s" s="2">
         <v>76</v>
       </c>
@@ -9034,13 +9024,13 @@
         <v>76</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>76</v>
+        <v>403</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>76</v>
+        <v>404</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>76</v>
@@ -9058,27 +9048,27 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>204</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9086,7 +9076,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>82</v>
@@ -9101,19 +9091,19 @@
         <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>380</v>
+        <v>97</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>383</v>
+        <v>273</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -9150,17 +9140,19 @@
         <v>76</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AC66" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>365</v>
+        <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>74</v>
@@ -9169,7 +9161,7 @@
         <v>82</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>385</v>
+        <v>94</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>95</v>
@@ -9177,20 +9169,18 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>82</v>
@@ -9205,19 +9195,19 @@
         <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>380</v>
+        <v>124</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>383</v>
+        <v>416</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>76</v>
@@ -9227,7 +9217,7 @@
         <v>76</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>76</v>
@@ -9242,11 +9232,13 @@
         <v>76</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>390</v>
+        <v>76</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>76</v>
@@ -9264,7 +9256,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>379</v>
+        <v>419</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
@@ -9273,18 +9265,18 @@
         <v>82</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>385</v>
+        <v>420</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9292,31 +9284,35 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>98</v>
+        <v>423</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>76</v>
       </c>
@@ -9340,13 +9336,11 @@
         <v>76</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>76</v>
+        <v>426</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>76</v>
@@ -9364,7 +9358,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>100</v>
+        <v>427</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>74</v>
@@ -9373,29 +9367,29 @@
         <v>82</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>393</v>
+        <v>428</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>76</v>
@@ -9407,18 +9401,20 @@
         <v>76</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>103</v>
+        <v>220</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>104</v>
+        <v>429</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>105</v>
+        <v>430</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>76</v>
       </c>
@@ -9442,86 +9438,86 @@
         <v>76</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>76</v>
+        <v>433</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>76</v>
+        <v>434</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>110</v>
+        <v>428</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>94</v>
+        <v>435</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>395</v>
+        <v>436</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>396</v>
+        <v>436</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>76</v>
+        <v>437</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>397</v>
+        <v>220</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>399</v>
+        <v>439</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>401</v>
+        <v>441</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>76</v>
@@ -9546,13 +9542,13 @@
         <v>76</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>76</v>
+        <v>442</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>76</v>
+        <v>443</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>76</v>
@@ -9570,13 +9566,13 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>94</v>
@@ -9585,12 +9581,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>403</v>
+        <v>444</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>404</v>
+        <v>444</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9601,38 +9597,36 @@
         <v>74</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>162</v>
+        <v>445</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>406</v>
+        <v>447</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>273</v>
+        <v>448</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>407</v>
+        <v>449</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q71" t="s" s="2">
-        <v>408</v>
-      </c>
+      <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
         <v>76</v>
       </c>
@@ -9652,13 +9646,13 @@
         <v>76</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>216</v>
+        <v>76</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>409</v>
+        <v>76</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>410</v>
+        <v>76</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>76</v>
@@ -9676,13 +9670,13 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>411</v>
+        <v>444</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>94</v>
@@ -9691,12 +9685,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>413</v>
+        <v>450</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9704,35 +9698,31 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>414</v>
+        <v>98</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>76</v>
       </c>
@@ -9780,7 +9770,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>417</v>
+        <v>100</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>74</v>
@@ -9789,54 +9779,52 @@
         <v>82</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>418</v>
+        <v>451</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>420</v>
+        <v>104</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>421</v>
+        <v>105</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>76</v>
       </c>
@@ -9845,7 +9833,7 @@
         <v>76</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>424</v>
+        <v>76</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>76</v>
@@ -9872,39 +9860,39 @@
         <v>76</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>425</v>
+        <v>110</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>426</v>
+        <v>94</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9912,7 +9900,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>82</v>
@@ -9927,20 +9915,18 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>162</v>
+        <v>453</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>415</v>
+        <v>455</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>76</v>
       </c>
@@ -9964,29 +9950,29 @@
         <v>76</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Y74" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>432</v>
+        <v>76</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="AC74" s="2"/>
       <c r="AD74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>76</v>
+        <v>359</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>74</v>
@@ -10001,14 +9987,16 @@
         <v>95</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C75" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="D75" t="s" s="2">
         <v>76</v>
       </c>
@@ -10017,32 +10005,30 @@
         <v>74</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>220</v>
+        <v>460</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>76</v>
       </c>
@@ -10066,13 +10052,13 @@
         <v>76</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>439</v>
+        <v>76</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>440</v>
+        <v>76</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>76</v>
@@ -10090,7 +10076,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>434</v>
+        <v>457</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>74</v>
@@ -10099,7 +10085,7 @@
         <v>82</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>441</v>
+        <v>94</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>95</v>
@@ -10107,21 +10093,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>443</v>
+        <v>76</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>76</v>
@@ -10133,20 +10119,16 @@
         <v>76</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>220</v>
+        <v>97</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>444</v>
+        <v>98</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>76</v>
       </c>
@@ -10170,13 +10152,13 @@
         <v>76</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>448</v>
+        <v>76</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>449</v>
+        <v>76</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>76</v>
@@ -10194,31 +10176,31 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>442</v>
+        <v>100</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10228,7 +10210,7 @@
         <v>75</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>76</v>
@@ -10237,20 +10219,18 @@
         <v>76</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>451</v>
+        <v>103</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>452</v>
+        <v>104</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>453</v>
+        <v>105</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>76</v>
       </c>
@@ -10286,19 +10266,19 @@
         <v>76</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>450</v>
+        <v>110</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>74</v>
@@ -10310,15 +10290,15 @@
         <v>94</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10326,30 +10306,32 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>98</v>
+        <v>317</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>76</v>
@@ -10398,7 +10380,7 @@
         <v>76</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>74</v>
@@ -10407,29 +10389,29 @@
         <v>82</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>76</v>
+        <v>321</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>76</v>
@@ -10438,19 +10420,19 @@
         <v>76</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>104</v>
+        <v>323</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>105</v>
+        <v>324</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>106</v>
+        <v>325</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10476,51 +10458,51 @@
         <v>76</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>76</v>
+        <v>326</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>76</v>
+        <v>327</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>110</v>
+        <v>328</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10531,10 +10513,10 @@
         <v>74</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>76</v>
@@ -10543,16 +10525,16 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>459</v>
+        <v>193</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>460</v>
+        <v>330</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>461</v>
+        <v>331</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>462</v>
+        <v>332</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10590,17 +10572,19 @@
         <v>76</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AC80" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>365</v>
+        <v>76</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>463</v>
+        <v>333</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>74</v>
@@ -10615,16 +10599,14 @@
         <v>95</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>76</v>
       </c>
@@ -10633,10 +10615,10 @@
         <v>74</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>76</v>
@@ -10645,16 +10627,16 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>466</v>
+        <v>97</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>460</v>
+        <v>335</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>467</v>
+        <v>336</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>462</v>
+        <v>337</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -10704,7 +10686,7 @@
         <v>76</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>463</v>
+        <v>338</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>74</v>
@@ -10719,14 +10701,16 @@
         <v>95</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>76</v>
       </c>
@@ -10738,24 +10722,26 @@
         <v>82</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>98</v>
+        <v>454</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>476</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>76</v>
@@ -10804,7 +10790,7 @@
         <v>76</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>100</v>
+        <v>457</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>74</v>
@@ -10813,51 +10799,49 @@
         <v>82</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>103</v>
+        <v>353</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>104</v>
+        <v>478</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>106</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>76</v>
@@ -10894,39 +10878,39 @@
         <v>76</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>110</v>
+        <v>480</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10949,16 +10933,16 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>97</v>
+        <v>482</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>317</v>
+        <v>483</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>318</v>
+        <v>484</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>319</v>
+        <v>485</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11008,27 +10992,27 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>320</v>
+        <v>486</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>321</v>
+        <v>94</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11039,28 +11023,28 @@
         <v>74</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>124</v>
+        <v>220</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>323</v>
+        <v>488</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>324</v>
+        <v>489</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>325</v>
+        <v>490</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11086,13 +11070,13 @@
         <v>76</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>326</v>
+        <v>491</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>327</v>
+        <v>492</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>76</v>
@@ -11110,7 +11094,7 @@
         <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>328</v>
+        <v>487</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>74</v>
@@ -11127,10 +11111,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11141,7 +11125,7 @@
         <v>74</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>76</v>
@@ -11150,20 +11134,18 @@
         <v>76</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>330</v>
+        <v>98</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>76</v>
@@ -11212,7 +11194,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>333</v>
+        <v>100</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -11221,29 +11203,29 @@
         <v>82</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>76</v>
@@ -11252,19 +11234,19 @@
         <v>76</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>335</v>
+        <v>104</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>336</v>
+        <v>105</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>337</v>
+        <v>106</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11302,49 +11284,47 @@
         <v>76</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>338</v>
+        <v>110</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>82</v>
@@ -11359,18 +11339,20 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>460</v>
+        <v>243</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>76</v>
       </c>
@@ -11379,7 +11361,7 @@
         <v>76</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>76</v>
+        <v>293</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>76</v>
@@ -11394,13 +11376,11 @@
         <v>76</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>76</v>
+        <v>497</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>76</v>
@@ -11418,13 +11398,13 @@
         <v>76</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>463</v>
+        <v>247</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>94</v>
@@ -11433,12 +11413,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11452,22 +11432,22 @@
         <v>82</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>359</v>
+        <v>97</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>484</v>
+        <v>98</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>485</v>
+        <v>99</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11518,7 +11498,7 @@
         <v>76</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>486</v>
+        <v>100</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>74</v>
@@ -11527,50 +11507,50 @@
         <v>82</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>488</v>
+        <v>103</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>489</v>
+        <v>104</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>490</v>
+        <v>105</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>491</v>
+        <v>106</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11608,39 +11588,39 @@
         <v>76</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>492</v>
+        <v>110</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11648,7 +11628,7 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>82</v>
@@ -11660,21 +11640,23 @@
         <v>76</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>220</v>
+        <v>124</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>494</v>
+        <v>258</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>495</v>
+        <v>259</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>76</v>
       </c>
@@ -11698,13 +11680,13 @@
         <v>76</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>497</v>
+        <v>76</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>498</v>
+        <v>76</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>76</v>
@@ -11722,7 +11704,7 @@
         <v>76</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>493</v>
+        <v>262</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>74</v>
@@ -11737,12 +11719,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11750,30 +11732,32 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>98</v>
+        <v>265</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>76</v>
@@ -11822,7 +11806,7 @@
         <v>76</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>100</v>
+        <v>268</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>74</v>
@@ -11831,52 +11815,54 @@
         <v>82</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>104</v>
+        <v>271</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>105</v>
+        <v>272</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>76</v>
       </c>
@@ -11912,39 +11898,39 @@
         <v>76</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>110</v>
+        <v>275</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11967,19 +11953,19 @@
         <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>502</v>
+        <v>279</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>76</v>
@@ -11989,7 +11975,7 @@
         <v>76</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>293</v>
+        <v>76</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>76</v>
@@ -12004,11 +11990,13 @@
         <v>76</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Y94" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z94" t="s" s="2">
-        <v>503</v>
+        <v>76</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>76</v>
@@ -12026,13 +12014,13 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>94</v>
@@ -12057,7 +12045,7 @@
         <v>74</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>76</v>
@@ -12066,19 +12054,23 @@
         <v>76</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>97</v>
+        <v>284</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>98</v>
+        <v>285</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>76</v>
       </c>
@@ -12126,7 +12118,7 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>100</v>
+        <v>289</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>74</v>
@@ -12135,13 +12127,13 @@
         <v>82</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>505</v>
       </c>
@@ -12150,37 +12142,39 @@
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>104</v>
+        <v>303</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>105</v>
+        <v>506</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>76</v>
       </c>
@@ -12216,39 +12210,39 @@
         <v>76</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>110</v>
+        <v>307</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12256,7 +12250,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>82</v>
@@ -12268,22 +12262,22 @@
         <v>76</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>124</v>
+        <v>220</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>258</v>
+        <v>508</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>259</v>
+        <v>509</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>260</v>
+        <v>510</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>261</v>
+        <v>511</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>76</v>
@@ -12308,13 +12302,13 @@
         <v>76</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>76</v>
+        <v>512</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>76</v>
+        <v>513</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>76</v>
@@ -12332,7 +12326,7 @@
         <v>76</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>262</v>
+        <v>507</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>74</v>
@@ -12347,12 +12341,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12360,32 +12354,30 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K98" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>265</v>
+        <v>98</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>76</v>
@@ -12434,7 +12426,7 @@
         <v>76</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>268</v>
+        <v>100</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>74</v>
@@ -12443,54 +12435,52 @@
         <v>82</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>271</v>
+        <v>104</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>76</v>
       </c>
@@ -12526,39 +12516,39 @@
         <v>76</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>275</v>
+        <v>110</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12566,10 +12556,10 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>83</v>
@@ -12581,19 +12571,19 @@
         <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>279</v>
+        <v>517</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>76</v>
@@ -12642,13 +12632,13 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>281</v>
+        <v>247</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>94</v>
@@ -12659,10 +12649,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12673,7 +12663,7 @@
         <v>74</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>76</v>
@@ -12682,23 +12672,19 @@
         <v>76</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>284</v>
+        <v>97</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>285</v>
+        <v>98</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>76</v>
       </c>
@@ -12746,7 +12732,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>289</v>
+        <v>100</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>74</v>
@@ -12755,54 +12741,52 @@
         <v>82</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>303</v>
+        <v>104</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>512</v>
+        <v>105</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>76</v>
       </c>
@@ -12838,39 +12822,39 @@
         <v>76</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>307</v>
+        <v>110</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12878,7 +12862,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>82</v>
@@ -12890,22 +12874,22 @@
         <v>76</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>220</v>
+        <v>124</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>514</v>
+        <v>258</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>515</v>
+        <v>259</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>516</v>
+        <v>260</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>517</v>
+        <v>261</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>76</v>
@@ -12930,13 +12914,13 @@
         <v>76</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>518</v>
+        <v>76</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>519</v>
+        <v>76</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>76</v>
@@ -12954,7 +12938,7 @@
         <v>76</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>513</v>
+        <v>262</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>74</v>
@@ -12969,12 +12953,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12988,24 +12972,26 @@
         <v>82</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>98</v>
+        <v>265</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>76</v>
@@ -13054,7 +13040,7 @@
         <v>76</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>100</v>
+        <v>268</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>74</v>
@@ -13063,52 +13049,54 @@
         <v>82</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>104</v>
+        <v>271</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>105</v>
+        <v>272</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>76</v>
       </c>
@@ -13144,39 +13132,39 @@
         <v>76</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>110</v>
+        <v>275</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13184,10 +13172,10 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>83</v>
@@ -13199,19 +13187,19 @@
         <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>523</v>
+        <v>279</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>76</v>
@@ -13260,13 +13248,13 @@
         <v>76</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>94</v>
@@ -13291,7 +13279,7 @@
         <v>74</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>76</v>
@@ -13300,19 +13288,23 @@
         <v>76</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>97</v>
+        <v>284</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>98</v>
+        <v>285</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>76</v>
       </c>
@@ -13360,7 +13352,7 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>100</v>
+        <v>289</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>74</v>
@@ -13369,13 +13361,13 @@
         <v>82</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
         <v>525</v>
       </c>
@@ -13384,37 +13376,39 @@
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>104</v>
+        <v>303</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>105</v>
+        <v>526</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O108" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>76</v>
       </c>
@@ -13450,39 +13444,39 @@
         <v>76</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>110</v>
+        <v>307</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13490,35 +13484,33 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>124</v>
+        <v>528</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>258</v>
+        <v>529</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>259</v>
+        <v>530</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>76</v>
       </c>
@@ -13566,7 +13558,7 @@
         <v>76</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>262</v>
+        <v>527</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>74</v>
@@ -13578,15 +13570,15 @@
         <v>94</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>95</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13597,28 +13589,28 @@
         <v>74</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>97</v>
+        <v>533</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>265</v>
+        <v>534</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>266</v>
+        <v>535</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>267</v>
+        <v>536</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13668,7 +13660,7 @@
         <v>76</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>268</v>
+        <v>532</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>74</v>
@@ -13680,15 +13672,15 @@
         <v>94</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>95</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13696,34 +13688,34 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>162</v>
+        <v>538</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>271</v>
+        <v>539</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>272</v>
+        <v>540</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>273</v>
+        <v>541</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>274</v>
+        <v>542</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>76</v>
@@ -13772,27 +13764,27 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>275</v>
+        <v>537</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>95</v>
+        <v>543</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13800,35 +13792,31 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>278</v>
+        <v>98</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>76</v>
       </c>
@@ -13876,7 +13864,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>281</v>
+        <v>100</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>74</v>
@@ -13885,29 +13873,29 @@
         <v>82</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>530</v>
+        <v>545</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>530</v>
+        <v>545</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>76</v>
@@ -13916,23 +13904,21 @@
         <v>76</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>284</v>
+        <v>103</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>285</v>
+        <v>104</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>286</v>
+        <v>105</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>76</v>
       </c>
@@ -13968,74 +13954,74 @@
         <v>76</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>289</v>
+        <v>110</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>531</v>
+        <v>546</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>531</v>
+        <v>546</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>76</v>
+        <v>547</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I114" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="J114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>303</v>
+        <v>548</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>305</v>
+        <v>106</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>306</v>
+        <v>190</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>76</v>
@@ -14084,27 +14070,27 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>307</v>
+        <v>550</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14115,7 +14101,7 @@
         <v>74</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>76</v>
@@ -14127,16 +14113,16 @@
         <v>76</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -14186,7 +14172,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
@@ -14195,18 +14181,18 @@
         <v>82</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>94</v>
+        <v>556</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>204</v>
+        <v>557</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14217,7 +14203,7 @@
         <v>74</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>76</v>
@@ -14229,16 +14215,16 @@
         <v>76</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -14288,7 +14274,7 @@
         <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
@@ -14297,18 +14283,18 @@
         <v>82</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>94</v>
+        <v>556</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>204</v>
+        <v>557</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14319,7 +14305,7 @@
         <v>74</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>76</v>
@@ -14331,19 +14317,19 @@
         <v>76</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>544</v>
+        <v>220</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>545</v>
+        <v>562</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>76</v>
@@ -14368,13 +14354,13 @@
         <v>76</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>76</v>
+        <v>566</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>76</v>
+        <v>567</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>76</v>
@@ -14392,27 +14378,27 @@
         <v>76</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>549</v>
+        <v>95</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14423,7 +14409,7 @@
         <v>74</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>76</v>
@@ -14435,16 +14421,20 @@
         <v>76</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>98</v>
+        <v>569</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>76</v>
       </c>
@@ -14468,13 +14458,13 @@
         <v>76</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>76</v>
+        <v>573</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>76</v>
+        <v>574</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>76</v>
@@ -14492,38 +14482,38 @@
         <v>76</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>100</v>
+        <v>568</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>551</v>
+        <v>575</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>551</v>
+        <v>575</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>76</v>
@@ -14535,18 +14525,20 @@
         <v>76</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>103</v>
+        <v>576</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>104</v>
+        <v>577</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>105</v>
+        <v>578</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O119" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>580</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>76</v>
       </c>
@@ -14582,75 +14574,73 @@
         <v>76</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>110</v>
+        <v>575</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>111</v>
+        <v>581</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>552</v>
+        <v>582</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>552</v>
+        <v>582</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>553</v>
+        <v>76</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>554</v>
+        <v>583</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>555</v>
+        <v>584</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>76</v>
       </c>
@@ -14698,27 +14688,27 @@
         <v>76</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>556</v>
+        <v>582</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14729,7 +14719,7 @@
         <v>74</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>76</v>
@@ -14738,19 +14728,19 @@
         <v>76</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>558</v>
+        <v>586</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>559</v>
+        <v>587</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>561</v>
+        <v>589</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -14800,27 +14790,27 @@
         <v>76</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>562</v>
+        <v>94</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>563</v>
+        <v>204</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14831,7 +14821,7 @@
         <v>74</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>76</v>
@@ -14840,19 +14830,19 @@
         <v>76</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>558</v>
+        <v>591</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>565</v>
+        <v>592</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>566</v>
+        <v>593</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>561</v>
+        <v>594</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14902,27 +14892,27 @@
         <v>76</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>562</v>
+        <v>94</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>563</v>
+        <v>204</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14933,7 +14923,7 @@
         <v>74</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>76</v>
@@ -14942,22 +14932,22 @@
         <v>76</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>220</v>
+        <v>538</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>568</v>
+        <v>596</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>569</v>
+        <v>597</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>570</v>
+        <v>598</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>571</v>
+        <v>599</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>76</v>
@@ -14982,13 +14972,13 @@
         <v>76</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>166</v>
+        <v>76</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>572</v>
+        <v>76</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>573</v>
+        <v>76</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>76</v>
@@ -15006,27 +14996,27 @@
         <v>76</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>95</v>
+        <v>600</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>574</v>
+        <v>601</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>574</v>
+        <v>601</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15037,7 +15027,7 @@
         <v>74</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>76</v>
@@ -15049,20 +15039,16 @@
         <v>76</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>220</v>
+        <v>97</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>575</v>
+        <v>98</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>76</v>
       </c>
@@ -15086,13 +15072,13 @@
         <v>76</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>579</v>
+        <v>76</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>580</v>
+        <v>76</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>76</v>
@@ -15110,38 +15096,38 @@
         <v>76</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>574</v>
+        <v>100</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>76</v>
@@ -15153,20 +15139,18 @@
         <v>76</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>582</v>
+        <v>103</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>583</v>
+        <v>104</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>584</v>
+        <v>105</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>586</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>76</v>
       </c>
@@ -15202,73 +15186,75 @@
         <v>76</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>581</v>
+        <v>110</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>587</v>
+        <v>111</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>76</v>
+        <v>547</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>589</v>
+        <v>548</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>590</v>
+        <v>549</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>76</v>
       </c>
@@ -15316,27 +15302,27 @@
         <v>76</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>588</v>
+        <v>550</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15344,10 +15330,10 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>76</v>
@@ -15359,18 +15345,20 @@
         <v>83</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>592</v>
+        <v>220</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O127" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>76</v>
       </c>
@@ -15394,13 +15382,13 @@
         <v>76</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>76</v>
+        <v>237</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>76</v>
+        <v>238</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>76</v>
@@ -15418,27 +15406,27 @@
         <v>76</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>204</v>
+        <v>95</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15449,7 +15437,7 @@
         <v>74</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>76</v>
@@ -15461,18 +15449,20 @@
         <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O128" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>76</v>
       </c>
@@ -15508,41 +15498,41 @@
         <v>76</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="AC128" s="2"/>
       <c r="AD128" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>204</v>
+        <v>95</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C129" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="D129" t="s" s="2">
         <v>76</v>
       </c>
@@ -15551,7 +15541,7 @@
         <v>74</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>76</v>
@@ -15563,19 +15553,19 @@
         <v>83</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>544</v>
+        <v>374</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>605</v>
+        <v>378</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>76</v>
@@ -15624,27 +15614,27 @@
         <v>76</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>606</v>
+        <v>95</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15741,10 +15731,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15843,45 +15833,45 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>553</v>
+        <v>76</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>103</v>
+        <v>391</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>554</v>
+        <v>392</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>555</v>
+        <v>620</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>106</v>
+        <v>394</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>190</v>
+        <v>395</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>76</v>
@@ -15930,27 +15920,27 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>556</v>
+        <v>396</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>610</v>
+        <v>621</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15958,7 +15948,7 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>82</v>
@@ -15967,30 +15957,32 @@
         <v>76</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J133" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>220</v>
+        <v>162</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>611</v>
+        <v>399</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>612</v>
+        <v>400</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>613</v>
+        <v>273</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>236</v>
+        <v>401</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q133" s="2"/>
+      <c r="Q133" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="R133" t="s" s="2">
         <v>76</v>
       </c>
@@ -16010,13 +16002,13 @@
         <v>76</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>237</v>
+        <v>403</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>238</v>
+        <v>404</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>76</v>
@@ -16034,10 +16026,10 @@
         <v>76</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>610</v>
+        <v>405</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>82</v>
@@ -16051,10 +16043,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16062,7 +16054,7 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G134" t="s" s="2">
         <v>82</v>
@@ -16077,19 +16069,19 @@
         <v>83</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>615</v>
+        <v>97</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>616</v>
+        <v>408</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>618</v>
+        <v>273</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>76</v>
@@ -16126,17 +16118,19 @@
         <v>76</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AC134" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD134" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>614</v>
+        <v>411</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>74</v>
@@ -16153,20 +16147,18 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>82</v>
@@ -16181,19 +16173,19 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>380</v>
+        <v>124</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>616</v>
+        <v>414</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>617</v>
+        <v>628</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>618</v>
+        <v>416</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>76</v>
@@ -16203,7 +16195,7 @@
         <v>76</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>76</v>
+        <v>418</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>76</v>
@@ -16242,7 +16234,7 @@
         <v>76</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>614</v>
+        <v>419</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>74</v>
@@ -16251,7 +16243,7 @@
         <v>82</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>94</v>
+        <v>420</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>95</v>
@@ -16259,10 +16251,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16270,7 +16262,7 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G136" t="s" s="2">
         <v>82</v>
@@ -16282,19 +16274,23 @@
         <v>76</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>98</v>
+        <v>423</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
+        <v>631</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P136" t="s" s="2">
         <v>76</v>
       </c>
@@ -16342,7 +16338,7 @@
         <v>76</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>100</v>
+        <v>427</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>74</v>
@@ -16351,29 +16347,29 @@
         <v>82</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>76</v>
@@ -16385,18 +16381,20 @@
         <v>76</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>103</v>
+        <v>220</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>104</v>
+        <v>633</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>105</v>
+        <v>634</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O137" s="2"/>
+        <v>635</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>76</v>
       </c>
@@ -16420,62 +16418,62 @@
         <v>76</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>76</v>
+        <v>433</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>76</v>
+        <v>434</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>110</v>
+        <v>632</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>94</v>
+        <v>435</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>76</v>
+        <v>437</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>76</v>
@@ -16484,22 +16482,22 @@
         <v>76</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>397</v>
+        <v>220</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>626</v>
+        <v>439</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>401</v>
+        <v>441</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>76</v>
@@ -16524,13 +16522,13 @@
         <v>76</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>76</v>
+        <v>442</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>76</v>
+        <v>443</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>76</v>
@@ -16548,13 +16546,13 @@
         <v>76</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>402</v>
+        <v>636</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>94</v>
@@ -16565,10 +16563,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>627</v>
+        <v>637</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16579,38 +16577,36 @@
         <v>74</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>405</v>
+        <v>638</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>406</v>
+        <v>639</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>273</v>
+        <v>541</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>407</v>
+        <v>542</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q139" t="s" s="2">
-        <v>408</v>
-      </c>
+      <c r="Q139" s="2"/>
       <c r="R139" t="s" s="2">
         <v>76</v>
       </c>
@@ -16630,13 +16626,13 @@
         <v>76</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>216</v>
+        <v>76</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>409</v>
+        <v>76</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>410</v>
+        <v>76</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>76</v>
@@ -16654,647 +16650,23 @@
         <v>76</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>411</v>
+        <v>637</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="140" hidden="true">
-      <c r="A140" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="P140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q140" s="2"/>
-      <c r="R140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="141" hidden="true">
-      <c r="A141" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E141" s="2"/>
-      <c r="F141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="P141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q141" s="2"/>
-      <c r="R141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S141" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="142" hidden="true">
-      <c r="A142" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E142" s="2"/>
-      <c r="F142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="P142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q142" s="2"/>
-      <c r="R142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="143" hidden="true">
-      <c r="A143" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E143" s="2"/>
-      <c r="F143" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K143" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L143" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="P143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q143" s="2"/>
-      <c r="R143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X143" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AG143" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI143" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AJ143" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="144" hidden="true">
-      <c r="A144" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="C144" s="2"/>
-      <c r="D144" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G144" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K144" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="P144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q144" s="2"/>
-      <c r="R144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X144" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="Z144" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AG144" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH144" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI144" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ144" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="145" hidden="true">
-      <c r="A145" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="C145" s="2"/>
-      <c r="D145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E145" s="2"/>
-      <c r="F145" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="L145" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="P145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q145" s="2"/>
-      <c r="R145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF145" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AG145" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ145" t="s" s="2">
         <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ145">
+  <autoFilter ref="A1:AJ139">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17304,7 +16676,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI144">
+  <conditionalFormatting sqref="A2:AI138">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:51:19+02:00</t>
+    <t>2026-06-26T18:38:01+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T18:38:01+02:00</t>
+    <t>2026-07-06T17:54:18+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T17:54:18+02:00</t>
+    <t>2026-07-22T15:49:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Head-Circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T15:49:40+02:00</t>
+    <t>2026-07-22T16:29:56+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
